--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260713_205015.xlsx
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
